--- a/QA_TEST_LIST.xlsx
+++ b/QA_TEST_LIST.xlsx
@@ -3767,17 +3767,17 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Escribe `76086428` (8 dígitos)</t>
+          <t>Escribe `76086428` (8 dígitos). Después clic fuera del input (blur).</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Quedan los 8 dígitos juntos, sin formato aún</t>
+          <t>✅ Mientras escribes → `76086428` juntos / borde neutro GRIS.  ✅ Después blur → sigue igual (`76086428`) — el formato PUNTOS+GUION sólo aparece cuando hay 9+ dígitos (8 cuerpo + DV), no antes.</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>El formato con puntos y guion se aplica cuando escribas el 9º dígito (el DV) o pegues un RUT completo</t>
+          <t>El pretty print **NO** se aplica aún; se necesita al menos un DV para poder hacer `XX.XXX.XXX-DV`.</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Después de `76086428`, escribe un `5` (el total es `760864285`)</t>
+          <t>Después de `76086428`, escribe un `5` (total `760864285`).  ⚠️ **LUEGO**: haz clic FUERA del campo (pierde foco / pulsa TAB).</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>El input se transforma automáticamente en **`76.086.428-5`** (con puntos y guion)</t>
+          <t>Durante escritura del 9º dígito → se ve `760864285` (sin puntos, sin guion, borde GRIS).  ✅ **Después del blur** → el valor se convierte en **`76.086.428-5`** (puntos y guion).  Borde VERDE ✔ + check verde.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Borde del input se pone verde ✔; aparece un check verde al final</t>
+          <t>**NO debe mostrar el formato `76.086.428-5` mientras sigues escribiendo; sólo cuando sales del campo** (onBlur).</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -3839,17 +3839,17 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Borra todo y escribe: `12345678k` (termina en k)</t>
+          <t>Borra todo y escribe `12345678k`.  ⚠️ **Después: clic FUERA del input** (pierde foco / TAB).</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>El input muestra **`12.345.678-K`**</t>
+          <t>✅ Mientras escribes → `12345678k` raw / borde gris.  ✅ Después del blur → **`12.345.678-K`** formateado.</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>La “k” se pasa a mayúscula y aparece como DV; el borde PUEDE quedar rojo si el DV no coincide matemáticamente — eso es normal</t>
+          <t>La “k” sólo se pasa a mayúscula **onBlur**, no antes. El DV visualmente coincide con lo que escribiste (no corregido silenciosamente). Si matemáticamente no coincide, después de blur el borde se pone ROJO.</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -3875,17 +3875,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Copia `760864285` (solo números, 9 dígitos) → Ctrl+V en el input</t>
+          <t>Copia `760864285` → Ctrl+V en el input. ⚠️ Luego **clic fuera** (pierde foco).</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Muestra **`76.086.428-5`** (aplicado el formato)</t>
+          <t>Después del pegado (antes blur) → se ve el texto raw pegado.  ✅ Después de blur → **`76.086.428-5`** formateado.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>No se pierde ningún dígito del texto pegado</t>
+          <t>No se pierde ningún dígito del texto pegado. El formato bonito (puntos/guion) se retrasa a blur, igual que la escritura a mano.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Copia `12-345-678-5` (muchos guiones) → pégalo</t>
+          <t>Copia `12-345-678-5` (muchos guiones) → pégalo.  ⚠️ Después: clic fuera / blur.</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Lo normaliza a **`12.345.678-5`**</t>
+          <t>Antes blur → se ve como hayas pegado.  ✅ Después blur → normaliza a **`12.345.678-5`** (1 solo guion + puntos).</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Los separadores de sobra se limpian y quedan puntos + un solo guion</t>
+          <t>Se limpian los separadores de sobra pero **sólo cuando pierde foco**.</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -4046,17 +4046,17 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Escribe `12.345.678-5` (borde ✔ verde). Pon el cursor al final. Pulsa **⌫ BACKSPACE** 1 vez.</t>
+          <t>(1) Escribe `12.345.678-5` y **haz clic FUERA** para activar formato+verde.  (2) Regresa al input, cursor al final y pulsa **⌫ BACKSPACE** 1 vez.</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>El valor pasa a ser **`12345678`** (solo el cuerpo; desaparecen el `-5` y los puntos). El borde deja de ser verde.</t>
+          <t>El valor pasa a ser **`12345678`** (solo cuerpo; sin puntos/guion). Durante la escritura (tienes foco) el borde se vuelve GRIS (no verde, no rojo).</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>**NO debe reaparecer el `-5` automáticamente.** Tiene que quedarse como lo dejaste.</t>
+          <t>**NO debe reaparecer el `-5` después del backspace.** Borrado escribe estado RAW; si luego **sales con blur** y es inválido → puedes poner borde ROJO (aceptable).</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -4082,17 +4082,17 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Cursor ENTRE el `8` y el `-` → pulsa ⌫ 1 vez</t>
+          <t>(1) RUT VALIDO, blur para tener verde. (2) Vuelve a entrar, cursor entre `8` y `-` → pulsa ⌫ 1 vez.</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>El input muestra **`123456785`** (9 dígitos seguidos, sin puntos ni guion)</t>
+          <t>Mientras sigues dentro del input → muestra solo **`123456785`** (números juntos, sin puntos ni guion, borde gris).</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>**NO debe reinsertarse el guion** al instante; deja la forma “números juntos”</t>
+          <t>**NO debe reinsertarse el guion y los puntos mientras estás escribiendo.** El pretty print sólo vuelve a aparecer **después de blur** (clic fuera).</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
@@ -4397,17 +4397,17 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Escribe `76.086.428-5`</t>
+          <t>Escribe `76.086.428-5` (o la versión raw `760864285`). ⚠️ **Finalmente: CLIC FUERA del input (blur).**</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Borde **VERDE** + ✔ check verde al final</t>
+          <t>✅ Mientras escribes → borde GRIS, sin check.  ✅ Después de blur → se formatea a `76.086.428-5` y borde **VERDE** + ✔ check verde.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>El RUT se considera VÁLIDO</t>
+          <t>**Validez y color verde NO aparecen mientras escribes; sólo al perder el foco.**</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -4428,22 +4428,22 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>RUT correcto de 7 dígitos + letra K</t>
+          <t>RUT correcto 7 dígitos + K</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Escribe `1000005K` o `1.000.005-K`</t>
+          <t>Escribe `1000005K`. Después **clic fuera** (blur).</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Borde **VERDE** + ✔; formato correcto</t>
+          <t>Mientras escribes → raw. Después blur → se convierte en **`1.000.005-K`** y borde **VERDE** ✔ (K mayúscula).</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>DV “K” mayúscula y válido matemáticamente</t>
+          <t>El K se normaliza a mayúsculas y el borde se pone VERDE — pero **sólo después de blur**.</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
@@ -4469,17 +4469,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Escribe `12.345.678-9` (el DV correcto para ese cuerpo sería `-5`, no `-9`)</t>
+          <t>Escribe `12.345.678-9` (DV correcto = `-5`). Después **haz clic FUERA del input (blur)**.</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Borde **ROJO** o mensaje “RUT inválido”; icono ✕ o sin check</t>
+          <t>✅ Mientras escribes → borde GRIS (sin rojo, sin verde).  ✅ Después de blur → borde **ROJO** ✕ o mensaje “RUT inválido”; el valor se muestra formateado con `-9` (tu DV erróneo visible).</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>El DV incorrecto que TÚ escribiste se MANTIENE visible (no debe silenciosamente cambiar el `-9` por `-5`)</t>
+          <t>**No debe poner ROJO mientras el usuario todavía está digitando el DV.** El rojo llega **sólo al perder el foco**. El DV que el usuario escribió (aunque sea `-9` erróneo) SE MANTIENE en pantalla (no silenciosamente corregido a -5).</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Formato automático</t>
+          <t>Formato automático (puntos de miles)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Escribe `12345678-5` (solo un guion, sin puntos)</t>
+          <t>Escribe `12345678-5` (solo 1 guion, sin puntos).  Después **clic FUERA (blur)**.</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Automáticamente lo muestra como **`12.345.678-5`**</t>
+          <t>✅ Mientras escribes → el texto sigue como lo escribiste (sin puntos).  ✅ Después blur → pasa a **`12.345.678-5`** (puntos de miles añadidos).</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Se añaden los puntos de separación de miles</t>
+          <t>Puntos se aplican sólo en blur; el usuario escribe sin alteraciones.</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -4536,22 +4536,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Caso “8 dígitos sin guion” (fix regresión 29.09.2026)</t>
+          <t>Caso “8 dígitos sin guion” (fix regresión 29.09)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Escribe SOLO `20779347` (8 dígitos, sin nada más) y añade luego el DV `7` → total `207793477`</t>
+          <t>Escribe SOLO `20779347` (8 díg.) y luego añade `7` (total `207793477`).  Luego **clic FUERA (blur)**.</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>El resultado formateado es **`20.779.347-7`** (8 dígitos de cuerpo)</t>
+          <t>Mientras escribes → texto raw `207793477` y borde neutro.  ✅ Después de blur → se formatea correctamente en **`20.779.347-7`** (8 dígitos cuerpo, no 7).</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>**NO debe formatear como `2.077.934-7`** (7 dígitos de cuerpo — este sería el bug antiguo)</t>
+          <t>**NO debe formatear como `2.077.934-7`** (antiguo bug 7 dígitos cuerpo). El pretty-print se aplica onBlur, no a mitad de escritura.</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -4577,17 +4577,17 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Escribe `1-9`</t>
+          <t>Escribe `1-9`. Luego **clic FUERA (blur)**.</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Borde ROJO / mensaje “inválido”</t>
+          <t>Mientras escribes → `1-9` raw, borde gris.  Después blur → se pone **ROJO** (marcado inválido) ✕.</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>No lo marca como verde (no existe un RUT chileno de cuerpo = 1 dígito)</t>
+          <t>**No marca ROJO mientras escribes; espera a blur.** (Si hiciera rojo inmediatamente tras escribir el 9, el formateador onBlur antiguo sería fantasma).</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -4613,17 +4613,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Escribe `000123456785` (rellenado con ceros a la izquierda)</t>
+          <t>Escribe `000123456785`. Después **clic FUERA (blur)**.</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Se limpia y muestra **`12.345.678-5`**</t>
+          <t>Mientras escribes → texto tal cual.  Después blur → limpia a **`12.345.678-5`** y normaliza.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Los ceros sobrantes del principio no se conservan</t>
+          <t>Limpieza ceros sólo se aplica onBlur.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -5094,22 +5094,22 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Pasar al siguiente campo con TAB</t>
+          <t>Pasar al siguiente campo con TAB → ¡triggers blur automático!</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Estando en el input RUT, pulsa TAB</t>
+          <t>Escribe `760864285` (sin formato) → ⚠️ NO pulses clic fuera → directamente pulsa **TAB** para ir al campo Nombre.</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>El foco salta al siguiente campo (Nombre) y el RUT conserva el valor correcto</t>
+          <t>TAB dispara implícitamente onBlur.  Por tanto: al salir al campo Nombre → el RUT se formatea en **`76.086.428-5`** y marca borde VERDE ✔ sin tener que hacer clic manualmente.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>No “salta de vuelta” al input RUT</t>
+          <t>El TAB funciona como “confirmación de escritura” (blur implícito). Es normal y deseado.</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -5130,22 +5130,22 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Pulsar ENTER dentro del input RUT</t>
+          <t>Pulsar ENTER dentro del input (sin blur previo)</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Si el RUT es VÁLIDO y términos OK</t>
+          <t>Escribe un RUT correcto (ej `760864285`).  **Marca términos.**  ⚠️ SIN hacer clic fuera (sin blur) pulsa ENTER directamente dentro del input.</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Inicia la evaluación (igual que si clicaras el botón)</t>
+          <t>El submit **no se bloquea** por falta de blur: el backup en `handleSubmit` aplica la validación on-the-fly si isValidRut aún es null.  Si el RUT es OK → evalúa normalmente; si es RUT inválido → toast.  Además, al terminar el submit el RUT queda con el formato pretty (ya que finalRutFormatted se guarda).</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Si el RUT es inválido, NO inicia nada y muestra error</t>
+          <t>**Comportamiento antiguo era válido sin blur pero ahora funciona gracias a la guardia adicional en handleSubmit que valida antes de mostrar toast.** No hay que pedirle al usuario que haga clic fuera para proceder.</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
